--- a/PLANILHA_CONSOLIDADA_K4.xlsx
+++ b/PLANILHA_CONSOLIDADA_K4.xlsx
@@ -42,8 +42,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'EXAME_PRIORITARIO'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NAMING'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FALE_CONOSCO'!$A$2:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'PROCESSOS_PATENTE'!$A$2:$S$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'PROCESSOS_DESENHO_INDUSTRIAL'!$A$2:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'PROCESSOS_PATENTE'!$A$1:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'PROCESSOS_DESENHO_INDUSTRIAL'!$A$1:$T$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ACOMP_MENSAL'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'DESPACHOS_MARCAS'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'DESPACHOS_PATENTES'!$A$2:$J$2</definedName>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="1">
@@ -560,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -640,7 +639,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -653,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -675,6 +673,7 @@
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,6 +682,11 @@
           <t>Nº do processo no formato BR NN NNNN NNNNNN-D. Vinculado ao histórico DESPACHOS_PATENTES.</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fase atual</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -781,9 +785,8 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
-  <autoFilter ref="A2:S2"/>
+  <autoFilter ref="A1:T2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -794,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -816,6 +819,7 @@
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -824,6 +828,11 @@
           <t>Nº do processo no formato BR 30 NNNN NNNNNN-D. Vinculado a DESPACHOS_DESENHO_INDUSTRIAL (pendente — ver item 15 dos próximos passos).</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fase atual</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -922,9 +931,8 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
-  <autoFilter ref="A2:S2"/>
+  <autoFilter ref="A1:T2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -935,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -984,7 +992,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -997,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1065,7 +1072,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1078,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1158,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1165,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1233,7 +1238,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1246,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1302,7 +1306,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1315,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1395,7 +1398,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1458,9 +1460,6 @@
           <t>Marcas</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Preencher com o nº da última edição RM processada com sucesso</t>
@@ -1473,9 +1472,6 @@
           <t>Patentes</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Preencher com o nº da última edição P processada com sucesso</t>
@@ -1488,9 +1484,6 @@
           <t>Desenho Industrial</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Preencher quando o módulo PDF for fechado (item 15)</t>
@@ -1509,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1696,7 +1689,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <autoFilter ref="A1:AD1"/>
   <dataValidations count="1">
@@ -5431,7 +5423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5559,7 +5551,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:S2"/>
   <dataValidations count="1">
@@ -5577,7 +5568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5681,7 +5672,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:O2"/>
   <dataValidations count="2">
@@ -5702,7 +5692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5806,7 +5796,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:O2"/>
   <dataValidations count="2">
@@ -5827,7 +5816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5943,7 +5932,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:Q2"/>
   <dataValidations count="1">
@@ -5961,7 +5949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6053,7 +6041,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A2:M2"/>
   <dataValidations count="1">
@@ -6071,7 +6058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6168,7 +6155,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6181,7 +6167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6248,7 +6234,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
